--- a/processing_scripts/Sulfide/2024/Raw Data/TEMPEST20240708_H2S.xlsx
+++ b/processing_scripts/Sulfide/2024/Raw Data/TEMPEST20240708_H2S.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arizonastateu-my.sharepoint.com/personal/amontg35_sundevils_asu_edu/Documents/Data/TEMPEST/Porewater/01_RawMicroplateData/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/readz_si_edu1/Documents/TEMPEST_Porewater/processing_scripts/Sulfide/2024/Raw Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{636099FF-8FA6-4738-89E3-C6BD92A401DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64A7357A-017A-4EE8-BF7D-2739E50FE574}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{217D31C7-3677-45E3-B772-062F6D24D7E9}"/>
+    <workbookView xWindow="-19320" yWindow="690" windowWidth="19440" windowHeight="14880" activeTab="3" xr2:uid="{217D31C7-3677-45E3-B772-062F6D24D7E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Lab Check" sheetId="1" r:id="rId1"/>
@@ -3665,9 +3665,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DA2490B-6EFA-4564-93D1-114757CFBA34}">
   <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -3678,7 +3678,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>0.11700000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>0.313</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>0.58499999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>0.746</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -4098,12 +4098,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AAD36DA-8916-4551-82D4-D35943EEAC40}">
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.26953125" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -4276,7 +4276,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>0</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>2</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>3</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>5</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -4824,7 +4824,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>0</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>1</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>2</v>
       </c>
@@ -5029,7 +5029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>3</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
@@ -5111,7 +5111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>5</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
@@ -5243,9 +5243,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{292D26F3-DC46-4856-B879-BEE519F34DB3}">
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -5286,7 +5286,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -5418,7 +5418,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -5462,7 +5462,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -5550,7 +5550,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -5638,7 +5638,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
@@ -5679,7 +5679,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>0</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
@@ -5761,7 +5761,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="37.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>2</v>
       </c>
@@ -5802,7 +5802,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>3</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>5</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -5966,7 +5966,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>0</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>1</v>
       </c>
@@ -6130,7 +6130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>2</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>3</v>
       </c>
@@ -6212,7 +6212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>5</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
@@ -6335,7 +6335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
@@ -6384,9 +6384,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B531F4E6-2BC7-4F8D-97B2-8C40592F78E1}">
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -6427,7 +6427,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -6603,7 +6603,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -6647,7 +6647,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -6735,7 +6735,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -6779,7 +6779,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>33</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>0</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>2</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>3</v>
       </c>
@@ -6984,7 +6984,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>5</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -7107,7 +7107,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="62.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -7148,7 +7148,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
@@ -7189,7 +7189,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>0</v>
       </c>
@@ -7230,7 +7230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>1</v>
       </c>
@@ -7271,7 +7271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>2</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>3</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>5</v>
       </c>
@@ -7435,7 +7435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
@@ -7476,7 +7476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>7</v>
       </c>
